--- a/docs/printable/金湖展贸中心-设备BOM清单-2026-05-21.xlsx
+++ b/docs/printable/金湖展贸中心-设备BOM清单-2026-05-21.xlsx
@@ -16,6 +16,7 @@
     <sheet name="6-网络" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="7-线缆" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="8-工具" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="9-灯具" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="¥#,##0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -104,6 +105,17 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -138,7 +150,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -160,11 +172,55 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -221,6 +277,14 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -835,6 +899,8 @@
           <t>项目合计 (不含 LED 屏体)</t>
         </is>
       </c>
+      <c r="B13" s="22" t="n"/>
+      <c r="C13" s="23" t="n"/>
       <c r="D13" s="11">
         <f>SUM(D5:D12)</f>
         <v/>
@@ -1047,6 +1113,1526 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>金湖展贸中心智能控制系统 · 9. 灯具一体化采购建议 (土建/装修预算)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>⚠ 此 sheet 仅作采购建议, 由装修方采购; 灯具必须 0-10V 调光款 + AC 220V 输入 + CRI ≥ 80</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>品类</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>中文规格</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>品牌中文</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>品牌英文</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>推荐型号</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>单价(¥)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>小计(¥)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>关键 spec</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>安装位置</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>9.1 LED 灯带 (8 路, 392m 总, DC 24V 接外置 HLG 电源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-STRIP-1</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>灯带</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>LED 灯带 24V (前厅 30m)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>木林森</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Mulinsen</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>5050 LED 24V 10W/m 暖白 3000K</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I6" s="9">
+        <f>G6*H6</f>
+        <v/>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>CRI 80+ · IP20 · 单段 ≤5m · 5 年保</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>1F 前厅吊顶</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-STRIP-2</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>灯带</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>LED 灯带 24V (展示区 15m)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>木林森</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Mulinsen</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>5050 LED 24V 10W/m 暖白</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I7" s="9">
+        <f>G7*H7</f>
+        <v/>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>1F F101-R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-STRIP-3</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>灯带</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>LED 灯带 24V (园区 12m)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>木林森</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Mulinsen</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>5050 LED 24V 10W/m 暖白</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I8" s="9">
+        <f>G8*H8</f>
+        <v/>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>1F F101-R3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-STRIP-4</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>灯带</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>LED 灯带 24V (走廊 130m)</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>木林森</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Mulinsen</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>5050 LED 24V 10W/m 中性 4000K</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>130</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I9" s="9">
+        <f>G9*H9</f>
+        <v/>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>走廊 IP54 防尘款</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>1F 走廊吊顶</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-STRIP-5</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>灯带</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>LED 灯带 24V (R7 重点 80m)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>木林森</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Mulinsen</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>5050 LED 24V 10W/m 暖白</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I10" s="9">
+        <f>G10*H10</f>
+        <v/>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>CRI 80+</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>1F F101-R7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-STRIP-6</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>灯带</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>LED 灯带 24V (F102 企业展位 20m)</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>木林森</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Mulinsen</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>5050 LED 24V 10W/m 暖白</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I11" s="9">
+        <f>G11*H11</f>
+        <v/>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>1F F102</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-STRIP-7</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>灯带</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>LED 灯带 24V (F104 物贸 20m)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>木林森</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Mulinsen</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>5050 LED 24V 10W/m 暖白</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I12" s="9">
+        <f>G12*H12</f>
+        <v/>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>1F F104</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-STRIP-8</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>灯带</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>LED 灯带 24V (2F 走廊 85m)</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>木林森</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Mulinsen</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>5050 LED 24V 10W/m 中性 4000K</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I13" s="9">
+        <f>G13*H13</f>
+        <v/>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>IP54</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>2F 走廊吊顶</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>9.2 LED 筒灯 / 射灯 (10 路, ~150 盏, AC 220V + 0-10V 调光款)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-DL-1F-1</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>筒灯</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>LED 筒灯 20W 0-10V 调光款</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>欧普</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>OPPLE</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>MK-A-20W (商照系列)</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="I15" s="9">
+        <f>G15*H15</f>
+        <v/>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>AC 220V · 0-10V · CRI 85 · 暖白 3000K · 开孔 90mm</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>1F F101-R2 (前厅周边)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-SL-1F-1</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>射灯</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>LED 射灯 12W 0-10V 调光款</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>欧普</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>OPPLE</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>GD-A-12W</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="I16" s="9">
+        <f>G16*H16</f>
+        <v/>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>AC 220V · 0-10V · 24° 中角度</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>1F F101-R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-DL-1F-2</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>筒灯</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>LED 筒灯 30W 0-10V (园区展示)</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>欧普</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>OPPLE</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>MK-A-30W</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="I17" s="9">
+        <f>G17*H17</f>
+        <v/>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>AC 220V · 0-10V · 暖白 · 开孔 110mm</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>1F F101-R3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-DL-1F-3</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>筒灯</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>LED 筒灯 20W 0-10V (走廊密集)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>欧普</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>OPPLE</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>MK-A-20W</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="I18" s="9">
+        <f>G18*H18</f>
+        <v/>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>走廊 4000K 中性光</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>1F F101-R5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-SL-1F-3</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>射灯</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>LED 射灯 15W 0-10V</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>欧普</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>OPPLE</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>GD-A-15W</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" s="9">
+        <f>G19*H19</f>
+        <v/>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>24° 中角度 4000K</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>1F F101-R5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-CL-1F-1</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>吸顶</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>LED 吸顶灯 30W 0-10V</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>欧普</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>OPPLE</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>吸顶圆盘 30W</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>180</v>
+      </c>
+      <c r="I20" s="9">
+        <f>G20*H20</f>
+        <v/>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>走廊节点 AC 220V · 0-10V</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>1F F101-R6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-DL-1F-103</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>筒灯</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>LED 筒灯 20W 0-10V</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>欧普</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>OPPLE</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>MK-A-20W</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="I21" s="9">
+        <f>G21*H21</f>
+        <v/>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>1F F103-R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-SL-1F-103</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>射灯</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>LED 射灯 15W 0-10V</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>欧普</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>OPPLE</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>GD-A-15W</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="I22" s="9">
+        <f>G22*H22</f>
+        <v/>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>展销区聚焦</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>1F F103-R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-DL-2F-1</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>筒灯</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>LED 筒灯 20W 0-10V (2F 前厅)</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>欧普</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>OPPLE</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>MK-A-20W</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="I23" s="9">
+        <f>G23*H23</f>
+        <v/>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>密集排列 · 暖白</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>2F F201-R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-DL-2F-2</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>筒灯</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>LED 筒灯 30W 0-10V (服务中心)</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>欧普</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>OPPLE</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>MK-A-30W</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="I24" s="9">
+        <f>G24*H24</f>
+        <v/>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>大瓦数高亮</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>2F F201-R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-DL-2F-3</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>筒灯</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>LED 筒灯 20W 0-10V (服务中心 + 配房)</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>欧普</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>OPPLE</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>MK-A-20W</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="I25" s="9">
+        <f>G25*H25</f>
+        <v/>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>2F F201-R3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-SL-2F-3</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>射灯</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>LED 射灯 15W 0-10V</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>欧普</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>OPPLE</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>GD-A-15W</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" s="9">
+        <f>G26*H26</f>
+        <v/>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>展项聚焦</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>2F F201-R3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>9.3 LED 吸顶灯 / 面板灯 (3 路, 44 盏 2F 办公区)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-PL-2F-1</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>面板</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>600×600 LED 面板灯 60W 0-10V</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>欧普</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>OPPLE</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>面板灯 60W</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>280</v>
+      </c>
+      <c r="I28" s="9">
+        <f>G28*H28</f>
+        <v/>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>集成吊顶 600×600 · 自然光 4000K</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>2F F202 共享办公</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-PL-2F-2</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>面板</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>600×600 LED 面板灯 60W 0-10V</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>欧普</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>OPPLE</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>面板灯 60W</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>280</v>
+      </c>
+      <c r="I29" s="9">
+        <f>G29*H29</f>
+        <v/>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>2F F203 产业研究</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-PL-2F-3</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>面板</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>600×600 LED 面板灯 60W 0-10V</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>欧普</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>OPPLE</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>面板灯 60W</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>280</v>
+      </c>
+      <c r="I30" s="9">
+        <f>G30*H30</f>
+        <v/>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>2F F204 指挥中心</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>9.4 灯箱 LED 模组 (12 ㎡)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-LB-1</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>灯箱</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>LED 灯箱模组 DC 24V 50W/㎡</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>装修方定制</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>24V 恒压 LED 模组拼接 600W</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I32" s="9">
+        <f>G32*H32</f>
+        <v/>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>装修方根据灯箱外壳尺寸定制 (12㎡ × ¥500/㎡)</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>1F F101-R3 灯箱位</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>9.5 格栅长条灯 (1 路, 35m, 0-10V 调光款)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>LIGHT-GR-1</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>格栅</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>LED 格栅长条灯 20W/m 0-10V</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>三雄极光</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>PAK</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>格栅灯条 1.2m × 30 节</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>280</v>
+      </c>
+      <c r="I34" s="9">
+        <f>G34*H34</f>
+        <v/>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>商照工程款 · AC 220V · 0-10V</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>1F F101-R7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>本表合计 (灯具一体化)</t>
+        </is>
+      </c>
+      <c r="I35" s="20">
+        <f>SUM(I5:I34)</f>
+        <v/>
+      </c>
+      <c r="J35" s="21" t="n"/>
+      <c r="K35" s="21" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>■ 重要说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>1. 此 sheet 的灯具采购**由装修/土建方负责**, 智能化方仅给规格建议. 此处单价 + 数量按现场实测数据估算, 实际以装修方报价为准.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>2. 推荐欧普 OPPLE 商照系列 (灯具一线 + A 股上市 + 京东天猫遍地是), 雷士 NVC / 三雄极光 PAK / 西顿 CDN 同档替代.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>3. ⚠ **所有筒灯/射灯/吸顶/面板灯采购合同必须明确写: "0-10V 调光款"**. 非调光款 / TRIAC 款无法接入我们的 LT-84A 系统.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>4. 灯带按 DC 24V 10W/m 主流款采购, 木林森 / 国星光电 (国产 LED 芯片龙头) 是供应链上游, 性价比最高.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>5. 灯箱 LED 模组由广告灯箱厂定制 (我们提供 12㎡ 面积 + 600W 总功率给厂家), 走 DC 24V 接 HLG-320H × 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>6. 格栅长条灯如果装修方选 AC 220V 一体化款 (0-10V 调光), 接 LT-84A 即可; 若选 DC 24V 灯条款则要另加 1 台 HLG 电源.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>7. 此 sheet 总价 ~¥3 万, **不计入智能化设备小计**, 是土建预算的一部分.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A31:K31"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1146,6 +2732,16 @@
           <t>1.1 中控主机</t>
         </is>
       </c>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="22" t="n"/>
+      <c r="K5" s="23" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1205,6 +2801,16 @@
           <t>1.2 控制平板</t>
         </is>
       </c>
+      <c r="B7" s="22" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="22" t="n"/>
+      <c r="K7" s="23" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1316,6 +2922,13 @@
           <t>本表合计</t>
         </is>
       </c>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="23" t="n"/>
       <c r="I10" s="20">
         <f>SUM(I5:I9)</f>
         <v/>
@@ -1434,6 +3047,16 @@
           <t>2.1 网关与协议转换</t>
         </is>
       </c>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="22" t="n"/>
+      <c r="K5" s="23" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1545,6 +3168,16 @@
           <t>2.2 LED 灯带 DALI 恒压电源 (DC 24V, MEANWELL 明纬)</t>
         </is>
       </c>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="23" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -2280,6 +3913,16 @@
           <t>2.3 灯具 0-10V 调光转换器 (DALI 转 0-10V, LTECH 雷特)</t>
         </is>
       </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="22" t="n"/>
+      <c r="K23" s="23" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -2443,6 +4086,13 @@
           <t>本表合计</t>
         </is>
       </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="23" t="n"/>
       <c r="I27" s="20">
         <f>SUM(I5:I26)</f>
         <v/>
@@ -2562,6 +4212,16 @@
           <t>3.1 LED 大屏控制器 (诺瓦 NovaStar)</t>
         </is>
       </c>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="22" t="n"/>
+      <c r="K5" s="23" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2673,6 +4333,16 @@
           <t>3.2 LED 屏体配件 (按面积单独询价)</t>
         </is>
       </c>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="23" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -2784,6 +4454,13 @@
           <t>本表合计</t>
         </is>
       </c>
+      <c r="B11" s="22" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="23" t="n"/>
       <c r="I11" s="20">
         <f>SUM(I5:I10)</f>
         <v/>
@@ -2902,6 +4579,16 @@
           <t>4.1 DSP 数字音频处理器</t>
         </is>
       </c>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="22" t="n"/>
+      <c r="K5" s="23" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2961,6 +4648,16 @@
           <t>4.2 功放与喇叭</t>
         </is>
       </c>
+      <c r="B7" s="22" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="22" t="n"/>
+      <c r="K7" s="23" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -3072,6 +4769,16 @@
           <t>4.3 麦克风 (无线 UHF, 推荐方案见 docs/WIRELESS_NETWORK.md)</t>
         </is>
       </c>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="23" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -3235,6 +4942,13 @@
           <t>本表合计</t>
         </is>
       </c>
+      <c r="B14" s="22" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="23" t="n"/>
       <c r="I14" s="20">
         <f>SUM(I5:I13)</f>
         <v/>
@@ -3354,6 +5068,16 @@
           <t>5.1 中央空调外机 (奥克斯 ARV-X9 商用 VRF)</t>
         </is>
       </c>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="22" t="n"/>
+      <c r="K5" s="23" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -3465,6 +5189,16 @@
           <t>5.2 空调网关 (Modbus TCP)</t>
         </is>
       </c>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="23" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -3524,6 +5258,16 @@
           <t>5.3 中央空调内机 1F (10 台, 全直流式低静压风管机)</t>
         </is>
       </c>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="23" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -4051,6 +5795,16 @@
           <t>5.4 中央空调内机 2F (12 台)</t>
         </is>
       </c>
+      <c r="B21" s="22" t="n"/>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="23" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -4682,6 +6436,16 @@
           <t>5.5 触摸屏线控器 (每台内机配 1 个)</t>
         </is>
       </c>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="22" t="n"/>
+      <c r="H34" s="22" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="22" t="n"/>
+      <c r="K34" s="23" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -4741,6 +6505,13 @@
           <t>本表合计</t>
         </is>
       </c>
+      <c r="B36" s="22" t="n"/>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="22" t="n"/>
+      <c r="F36" s="22" t="n"/>
+      <c r="G36" s="22" t="n"/>
+      <c r="H36" s="23" t="n"/>
       <c r="I36" s="20">
         <f>SUM(I5:I35)</f>
         <v/>
@@ -4753,8 +6524,8 @@
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A21:K21"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A8:K8"/>
@@ -4862,6 +6633,16 @@
           <t>6.1 核心网络设备</t>
         </is>
       </c>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="22" t="n"/>
+      <c r="K5" s="23" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -4973,6 +6754,16 @@
           <t>6.2 无线 (可选, 详见 docs/WIRELESS_NETWORK.md)</t>
         </is>
       </c>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="23" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -5136,6 +6927,16 @@
           <t>6.3 不间断电源 UPS</t>
         </is>
       </c>
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="23" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -5195,6 +6996,16 @@
           <t>6.4 机柜与配电</t>
         </is>
       </c>
+      <c r="B14" s="22" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="23" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -5306,6 +7117,13 @@
           <t>本表合计</t>
         </is>
       </c>
+      <c r="B17" s="22" t="n"/>
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="23" t="n"/>
       <c r="I17" s="20">
         <f>SUM(I5:I16)</f>
         <v/>
@@ -5426,6 +7244,16 @@
           <t>7.1 网线</t>
         </is>
       </c>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="22" t="n"/>
+      <c r="K5" s="23" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -5537,6 +7365,16 @@
           <t>7.2 DALI 与 RS485 信号线</t>
         </is>
       </c>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="23" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -5700,6 +7538,16 @@
           <t>7.3 强电与音频线</t>
         </is>
       </c>
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="23" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -6019,6 +7867,16 @@
           <t>7.4 接头与小件</t>
         </is>
       </c>
+      <c r="B19" s="22" t="n"/>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="22" t="n"/>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="22" t="n"/>
+      <c r="K19" s="23" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -6130,6 +7988,13 @@
           <t>本表合计</t>
         </is>
       </c>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="23" t="n"/>
       <c r="I22" s="20">
         <f>SUM(I5:I21)</f>
         <v/>
@@ -6666,6 +8531,13 @@
           <t>本表合计</t>
         </is>
       </c>
+      <c r="B13" s="22" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="22" t="n"/>
+      <c r="H13" s="23" t="n"/>
       <c r="I13" s="20">
         <f>SUM(I5:I12)</f>
         <v/>

--- a/docs/printable/金湖展贸中心-设备BOM清单-2026-05-21.xlsx
+++ b/docs/printable/金湖展贸中心-设备BOM清单-2026-05-21.xlsx
@@ -1212,6 +1212,16 @@
           <t>9.1 LED 灯带 (8 路, 392m 总, DC 24V 接外置 HLG 电源)</t>
         </is>
       </c>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="22" t="n"/>
+      <c r="K5" s="23" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1635,6 +1645,16 @@
           <t>9.2 LED 筒灯 / 射灯 (10 路, ~150 盏, AC 220V + 0-10V 调光款)</t>
         </is>
       </c>
+      <c r="B14" s="22" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="23" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -2266,6 +2286,16 @@
           <t>9.3 LED 吸顶灯 / 面板灯 (3 路, 44 盏 2F 办公区)</t>
         </is>
       </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="22" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="22" t="n"/>
+      <c r="K27" s="23" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -2429,6 +2459,16 @@
           <t>9.4 灯箱 LED 模组 (12 ㎡)</t>
         </is>
       </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="22" t="n"/>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="22" t="n"/>
+      <c r="K31" s="23" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -2488,6 +2528,16 @@
           <t>9.5 格栅长条灯 (1 路, 35m, 0-10V 调光款)</t>
         </is>
       </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="22" t="n"/>
+      <c r="H33" s="22" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="22" t="n"/>
+      <c r="K33" s="23" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -2547,6 +2597,13 @@
           <t>本表合计 (灯具一体化)</t>
         </is>
       </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="22" t="n"/>
+      <c r="F35" s="22" t="n"/>
+      <c r="G35" s="22" t="n"/>
+      <c r="H35" s="23" t="n"/>
       <c r="I35" s="20">
         <f>SUM(I5:I34)</f>
         <v/>
@@ -2619,8 +2676,8 @@
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A33:K33"/>
     <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A42:K42"/>
     <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A42:K42"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A44:K44"/>
@@ -4975,7 +5032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5005,6 +5062,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5203,7 +5261,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>HVAC-GW-1</t>
+          <t>HVAC-GW-1F</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -5213,29 +5271,29 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>空调 Modbus TCP 通讯网关</t>
+          <t>1F TCP 集控网关</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>奥克斯</t>
+          <t>中弘</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>AUX</t>
+          <t>ZHONGHONG</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>CCM-270B</t>
+          <t>B 集控网关 TCP 款</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="I9" s="9">
         <f>G9*H9</f>
@@ -5243,7 +5301,7 @@
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>单 slaveId 多内机 · 64 内机上限 · Modbus TCP:502</t>
+          <t>MODBUS-TCP V3.2 · IP 192.168.50.51 · 64 内机上限 · DC 12V/1A 供电 · 直接接交换机 (省 USR-TCP232)</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
@@ -5253,78 +5311,78 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>HVAC-GW-2F</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>空调</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>2F TCP 集控网关</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>中弘</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>ZHONGHONG</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>B 集控网关 TCP 款</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I10" s="9">
+        <f>G10*H10</f>
+        <v/>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>同上 · IP 192.168.50.52 · 挂 2F 外机 (12 内机 n=0..11)</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>2F 公共电箱 F201</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>5.3 中央空调内机 1F (10 台, 全直流式低静压风管机)</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="22" t="n"/>
-      <c r="I10" s="22" t="n"/>
-      <c r="J10" s="22" t="n"/>
-      <c r="K10" s="23" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>HVAC-1F-1</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>空调内机 (企业展位 #1)</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>奥克斯</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>AUX</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>DLR-63F/DCDQH</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I11" s="9">
-        <f>G11*H11</f>
-        <v/>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>1.8kW</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>1F 企业展位</t>
-        </is>
-      </c>
+      <c r="B11" s="22" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="22" t="n"/>
+      <c r="K11" s="23" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>HVAC-1F-2</t>
+          <t>HVAC-1F-1</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -5334,7 +5392,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (企业展位 #2)</t>
+          <t>空调内机 (企业展位 #1)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -5359,7 +5417,7 @@
         <v>3000</v>
       </c>
       <c r="I12" s="9">
-        <f>G12*H12</f>
+        <f>G11*H11</f>
         <v/>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -5376,7 +5434,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>HVAC-1F-3</t>
+          <t>HVAC-1F-2</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -5386,7 +5444,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (企业展位 #3)</t>
+          <t>空调内机 (企业展位 #2)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -5411,7 +5469,7 @@
         <v>3000</v>
       </c>
       <c r="I13" s="9">
-        <f>G13*H13</f>
+        <f>G12*H12</f>
         <v/>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -5428,7 +5486,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>HVAC-1F-4</t>
+          <t>HVAC-1F-3</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -5438,7 +5496,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (直播间)</t>
+          <t>空调内机 (企业展位 #3)</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -5453,34 +5511,34 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>DLR-71F/DCDQH</t>
+          <t>DLR-63F/DCDQH</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>3300</v>
+        <v>3000</v>
       </c>
       <c r="I14" s="9">
-        <f>G14*H14</f>
+        <f>G13*H13</f>
         <v/>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>2kW</t>
+          <t>1.8kW</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>1F 直播间</t>
+          <t>1F 企业展位</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>HVAC-1F-5</t>
+          <t>HVAC-1F-4</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -5490,7 +5548,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (外贸交易展示区 #1)</t>
+          <t>空调内机 (直播间)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -5515,7 +5573,7 @@
         <v>3300</v>
       </c>
       <c r="I15" s="9">
-        <f>G15*H15</f>
+        <f>G14*H14</f>
         <v/>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -5525,14 +5583,14 @@
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>1F 外贸交易展示区</t>
+          <t>1F 直播间</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>HVAC-1F-6</t>
+          <t>HVAC-1F-5</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -5542,7 +5600,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (外贸交易展示区 #2)</t>
+          <t>空调内机 (外贸交易展示区 #1)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -5557,17 +5615,17 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>DLR-80F/DCDQH</t>
+          <t>DLR-71F/DCDQH</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="I16" s="9">
-        <f>G16*H16</f>
+        <f>G15*H15</f>
         <v/>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -5584,7 +5642,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>HVAC-1F-7</t>
+          <t>HVAC-1F-6</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -5594,7 +5652,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (园区展示)</t>
+          <t>空调内机 (外贸交易展示区 #2)</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -5609,34 +5667,34 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>DLR-90F/DCDQH</t>
+          <t>DLR-80F/DCDQH</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="I17" s="9">
-        <f>G17*H17</f>
+        <f>G16*H16</f>
         <v/>
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>2.2kW</t>
+          <t>2kW</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>1F 园区展示</t>
+          <t>1F 外贸交易展示区</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>HVAC-1F-8</t>
+          <t>HVAC-1F-7</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -5646,7 +5704,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (路演发布洽谈区 #1)</t>
+          <t>空调内机 (园区展示)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -5661,17 +5719,17 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>DLR-100F/DCDQH</t>
+          <t>DLR-90F/DCDQH</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="I18" s="9">
-        <f>G18*H18</f>
+        <f>G17*H17</f>
         <v/>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -5681,14 +5739,14 @@
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>1F 路演发布洽谈区</t>
+          <t>1F 园区展示</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>HVAC-1F-9</t>
+          <t>HVAC-1F-8</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -5698,7 +5756,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (路演发布洽谈区 #2)</t>
+          <t>空调内机 (路演发布洽谈区 #1)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -5713,17 +5771,17 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>DLR-112F/DCDQH</t>
+          <t>DLR-100F/DCDQH</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="I19" s="9">
-        <f>G19*H19</f>
+        <f>G18*H18</f>
         <v/>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -5740,7 +5798,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>HVAC-1F-10</t>
+          <t>HVAC-1F-9</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -5750,7 +5808,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (企业综合展销区)</t>
+          <t>空调内机 (路演发布洽谈区 #2)</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -5765,103 +5823,103 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>DLR-125F/DCDQH</t>
+          <t>DLR-112F/DCDQH</t>
         </is>
       </c>
       <c r="G20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I20" s="9">
+        <f>G19*H19</f>
+        <v/>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>2.2kW</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>1F 路演发布洽谈区</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>HVAC-1F-10</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>空调</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>空调内机 (企业综合展销区)</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>奥克斯</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>DLR-125F/DCDQH</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="9" t="n">
         <v>5500</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I21" s="9">
         <f>G20*H20</f>
         <v/>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>2.2kW</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>1F 企业综合展销区</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>5.4 中央空调内机 2F (12 台)</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n"/>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="22" t="n"/>
-      <c r="F21" s="22" t="n"/>
-      <c r="G21" s="22" t="n"/>
-      <c r="H21" s="22" t="n"/>
-      <c r="I21" s="22" t="n"/>
-      <c r="J21" s="22" t="n"/>
-      <c r="K21" s="23" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>HVAC-2F-11</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>空调内机 (集团产业管理中心)</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>奥克斯</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>AUX</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>DLR-90F/DCDQH</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I22" s="9">
-        <f>G22*H22</f>
-        <v/>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>2.2kW</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>2F 集团产业管理中心</t>
-        </is>
-      </c>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="22" t="n"/>
+      <c r="K22" s="23" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>HVAC-2F-12</t>
+          <t>HVAC-2F-11</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -5871,7 +5929,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (投资决策中心)</t>
+          <t>空调内机 (集团产业管理中心)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -5896,7 +5954,7 @@
         <v>4000</v>
       </c>
       <c r="I23" s="9">
-        <f>G23*H23</f>
+        <f>G22*H22</f>
         <v/>
       </c>
       <c r="J23" s="8" t="inlineStr">
@@ -5906,14 +5964,14 @@
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>2F 投资决策中心</t>
+          <t>2F 集团产业管理中心</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>HVAC-2F-13</t>
+          <t>HVAC-2F-12</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -5923,7 +5981,7 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (会议室)</t>
+          <t>空调内机 (投资决策中心)</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -5948,7 +6006,7 @@
         <v>4000</v>
       </c>
       <c r="I24" s="9">
-        <f>G24*H24</f>
+        <f>G23*H23</f>
         <v/>
       </c>
       <c r="J24" s="8" t="inlineStr">
@@ -5958,14 +6016,14 @@
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>2F 会议室</t>
+          <t>2F 投资决策中心</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>HVAC-2F-14</t>
+          <t>HVAC-2F-13</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -5975,7 +6033,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (共享办公室 #1)</t>
+          <t>空调内机 (会议室)</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -6000,7 +6058,7 @@
         <v>4000</v>
       </c>
       <c r="I25" s="9">
-        <f>G25*H25</f>
+        <f>G24*H24</f>
         <v/>
       </c>
       <c r="J25" s="8" t="inlineStr">
@@ -6010,14 +6068,14 @@
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>2F 共享办公室</t>
+          <t>2F 会议室</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>HVAC-2F-15</t>
+          <t>HVAC-2F-14</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -6027,7 +6085,7 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (共享办公室 #2)</t>
+          <t>空调内机 (共享办公室 #1)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -6052,7 +6110,7 @@
         <v>4000</v>
       </c>
       <c r="I26" s="9">
-        <f>G26*H26</f>
+        <f>G25*H25</f>
         <v/>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -6069,7 +6127,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>HVAC-2F-16</t>
+          <t>HVAC-2F-15</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -6079,7 +6137,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (企业服务中心 #1)</t>
+          <t>空调内机 (共享办公室 #2)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -6104,7 +6162,7 @@
         <v>4000</v>
       </c>
       <c r="I27" s="9">
-        <f>G27*H27</f>
+        <f>G26*H26</f>
         <v/>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -6114,14 +6172,14 @@
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>2F 企业服务中心</t>
+          <t>2F 共享办公室</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>HVAC-2F-17</t>
+          <t>HVAC-2F-16</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -6131,7 +6189,7 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (企业服务中心 #2)</t>
+          <t>空调内机 (企业服务中心 #1)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -6156,7 +6214,7 @@
         <v>4000</v>
       </c>
       <c r="I28" s="9">
-        <f>G28*H28</f>
+        <f>G27*H27</f>
         <v/>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -6173,7 +6231,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>HVAC-2F-18</t>
+          <t>HVAC-2F-17</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -6183,7 +6241,7 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (运营指挥中心 #1)</t>
+          <t>空调内机 (企业服务中心 #2)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -6208,7 +6266,7 @@
         <v>4000</v>
       </c>
       <c r="I29" s="9">
-        <f>G29*H29</f>
+        <f>G28*H28</f>
         <v/>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -6218,14 +6276,14 @@
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>2F 运营指挥中心</t>
+          <t>2F 企业服务中心</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>HVAC-2F-19</t>
+          <t>HVAC-2F-18</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -6235,7 +6293,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (运营指挥中心 #2)</t>
+          <t>空调内机 (运营指挥中心 #1)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -6260,7 +6318,7 @@
         <v>4000</v>
       </c>
       <c r="I30" s="9">
-        <f>G30*H30</f>
+        <f>G29*H29</f>
         <v/>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -6277,7 +6335,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>HVAC-2F-20</t>
+          <t>HVAC-2F-19</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -6287,7 +6345,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (前厅 #1)</t>
+          <t>空调内机 (运营指挥中心 #2)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -6302,17 +6360,17 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>DLR-100F/DCDQH</t>
+          <t>DLR-90F/DCDQH</t>
         </is>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="I31" s="9">
-        <f>G31*H31</f>
+        <f>G30*H30</f>
         <v/>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -6322,14 +6380,14 @@
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>2F 前厅</t>
+          <t>2F 运营指挥中心</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>HVAC-2F-21</t>
+          <t>HVAC-2F-20</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -6339,7 +6397,7 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (前厅 #2)</t>
+          <t>空调内机 (前厅 #1)</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -6364,7 +6422,7 @@
         <v>4500</v>
       </c>
       <c r="I32" s="9">
-        <f>G32*H32</f>
+        <f>G31*H31</f>
         <v/>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -6381,7 +6439,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>HVAC-2F-22</t>
+          <t>HVAC-2F-21</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -6391,7 +6449,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>空调内机 (产业研究中心)</t>
+          <t>空调内机 (前厅 #2)</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -6416,108 +6474,160 @@
         <v>4500</v>
       </c>
       <c r="I33" s="9">
+        <f>G32*H32</f>
+        <v/>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>2.2kW</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>2F 前厅</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>HVAC-2F-22</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>空调</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>空调内机 (产业研究中心)</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>奥克斯</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>DLR-100F/DCDQH</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I34" s="9">
         <f>G33*H33</f>
         <v/>
       </c>
-      <c r="J33" s="8" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>2.2kW</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
+      <c r="K34" s="8" t="inlineStr">
         <is>
           <t>2F 产业研究中心</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>5.5 触摸屏线控器 (每台内机配 1 个)</t>
         </is>
       </c>
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="22" t="n"/>
-      <c r="E34" s="22" t="n"/>
-      <c r="F34" s="22" t="n"/>
-      <c r="G34" s="22" t="n"/>
-      <c r="H34" s="22" t="n"/>
-      <c r="I34" s="22" t="n"/>
-      <c r="J34" s="22" t="n"/>
-      <c r="K34" s="23" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="22" t="n"/>
+      <c r="F35" s="22" t="n"/>
+      <c r="G35" s="22" t="n"/>
+      <c r="H35" s="22" t="n"/>
+      <c r="I35" s="22" t="n"/>
+      <c r="J35" s="22" t="n"/>
+      <c r="K35" s="23" t="n"/>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>HVAC-CTRL</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>空调</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>触摸屏线控器</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>奥克斯</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>AUX</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>XK10-DL-AUX (内销)</t>
         </is>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G36" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="H35" s="9" t="n">
+      <c r="H36" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="I35" s="9">
+      <c r="I36" s="9">
         <f>G35*H35</f>
         <v/>
       </c>
-      <c r="J35" s="8" t="inlineStr">
+      <c r="J36" s="8" t="inlineStr">
         <is>
           <t>每台内机配 1 个, 现场可手动操控</t>
         </is>
       </c>
-      <c r="K35" s="8" t="inlineStr">
+      <c r="K36" s="8" t="inlineStr">
         <is>
           <t>各内机旁</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>本表合计</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n"/>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="22" t="n"/>
-      <c r="E36" s="22" t="n"/>
-      <c r="F36" s="22" t="n"/>
-      <c r="G36" s="22" t="n"/>
-      <c r="H36" s="23" t="n"/>
-      <c r="I36" s="20">
-        <f>SUM(I5:I35)</f>
-        <v/>
-      </c>
-      <c r="J36" s="21" t="n"/>
-      <c r="K36" s="21" t="n"/>
+      <c r="B37" s="22" t="n"/>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="22" t="n"/>
+      <c r="F37" s="22" t="n"/>
+      <c r="G37" s="22" t="n"/>
+      <c r="H37" s="23" t="n"/>
+      <c r="I37" s="20">
+        <f>SUM(I5:I36)</f>
+        <v/>
+      </c>
+      <c r="J37" s="21" t="n"/>
+      <c r="K37" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/docs/printable/金湖展贸中心-设备BOM清单-2026-05-21.xlsx
+++ b/docs/printable/金湖展贸中心-设备BOM清单-2026-05-21.xlsx
@@ -4176,7 +4176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4206,6 +4206,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4323,7 +4324,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>6.5M 像素 · 10×RJ45 · HDMI×2+DVI+SDI · 1U 机架</t>
+          <t>HDMI1 输入接 GK9000 中控主机 HDMI 输出 (省独立 NUC 播控主机). 6.5M 像素 · 10×RJ45 · HDMI×2+DVI+SDI · 1U 机架</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
@@ -4333,78 +4334,78 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>LED-PLAYER-1</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>3.2 LED 屏体配件 (按面积单独询价)</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="22" t="n"/>
+      <c r="K7" s="23" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>LED-RECV</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>LED</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>LED 播控主机 (媒体播放)</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>英特尔</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>NUC11</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I7" s="9">
-        <f>G7*H7</f>
-        <v/>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Win10 + ViPlex Express · HDMI 输出到 VX1000</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>1F 主控室机柜</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>3.2 LED 屏体配件 (按面积单独询价)</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="22" t="n"/>
-      <c r="F8" s="22" t="n"/>
-      <c r="G8" s="22" t="n"/>
-      <c r="H8" s="22" t="n"/>
-      <c r="I8" s="22" t="n"/>
-      <c r="J8" s="22" t="n"/>
-      <c r="K8" s="23" t="n"/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>LED 接收卡 (按张计)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>诺瓦星云</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>NovaStar</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>A4s / A8s</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="I8" s="9">
+        <f>G9*H9</f>
+        <v/>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>每张接 65 万像素 LED 模组, 数量按屏估算</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>屏幕内部</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>LED-RECV</t>
+          <t>LED-MODULE</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -4414,117 +4415,66 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>LED 接收卡 (按张计)</t>
+          <t>LED 显示模组 (按㎡计)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>诺瓦星云</t>
+          <t>灯具厂家</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>NovaStar</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>A4s / A8s</t>
+          <t>按 P 间距选 P1.8/P2.5/P3</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I9" s="9">
-        <f>G9*H9</f>
+        <f>G10*H10</f>
         <v/>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>每张接 65 万像素 LED 模组, 数量按屏估算</t>
+          <t>AC 220V LED 模组, 按现场面积报价</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>屏幕内部</t>
+          <t>1F/2F 大屏区</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>LED-MODULE</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>LED 显示模组 (按㎡计)</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>灯具厂家</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>按 P 间距选 P1.8/P2.5/P3</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="9">
-        <f>G10*H10</f>
-        <v/>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>AC 220V LED 模组, 按现场面积报价</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>1F/2F 大屏区</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>本表合计</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="22" t="n"/>
-      <c r="G11" s="22" t="n"/>
-      <c r="H11" s="23" t="n"/>
-      <c r="I11" s="20">
-        <f>SUM(I5:I10)</f>
-        <v/>
-      </c>
-      <c r="J11" s="21" t="n"/>
-      <c r="K11" s="21" t="n"/>
-    </row>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="23" t="n"/>
+      <c r="I10" s="20">
+        <f>SUM(I5:I9)</f>
+        <v/>
+      </c>
+      <c r="J10" s="21" t="n"/>
+      <c r="K10" s="21" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:K2"/>
@@ -5062,7 +5012,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5316,51 +5265,16 @@
           <t>HVAC-GW-2F</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>2F TCP 集控网关</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>中弘</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>ZHONGHONG</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>B 集控网关 TCP 款</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I10" s="9">
-        <f>G10*H10</f>
-        <v/>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>同上 · IP 192.168.50.52 · 挂 2F 外机 (12 内机 n=0..11)</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>2F 公共电箱 F201</t>
-        </is>
-      </c>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="23" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
@@ -5853,51 +5767,16 @@
           <t>HVAC-1F-10</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>空调内机 (企业综合展销区)</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>奥克斯</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>AUX</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>DLR-125F/DCDQH</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>5500</v>
-      </c>
-      <c r="I21" s="9">
-        <f>G20*H20</f>
-        <v/>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>2.2kW</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>1F 企业综合展销区</t>
-        </is>
-      </c>
+      <c r="B21" s="22" t="n"/>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="23" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
@@ -6494,51 +6373,16 @@
           <t>HVAC-2F-22</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>空调内机 (产业研究中心)</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>奥克斯</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>AUX</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>DLR-100F/DCDQH</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="9" t="n">
-        <v>4500</v>
-      </c>
-      <c r="I34" s="9">
-        <f>G33*H33</f>
-        <v/>
-      </c>
-      <c r="J34" s="8" t="inlineStr">
-        <is>
-          <t>2.2kW</t>
-        </is>
-      </c>
-      <c r="K34" s="8" t="inlineStr">
-        <is>
-          <t>2F 产业研究中心</t>
-        </is>
-      </c>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="22" t="n"/>
+      <c r="H34" s="22" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="22" t="n"/>
+      <c r="K34" s="23" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
@@ -6563,37 +6407,13 @@
           <t>HVAC-CTRL</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>触摸屏线控器</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>奥克斯</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>AUX</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>XK10-DL-AUX (内销)</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="H36" s="9" t="n">
-        <v>200</v>
-      </c>
+      <c r="B36" s="22" t="n"/>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="22" t="n"/>
+      <c r="F36" s="22" t="n"/>
+      <c r="G36" s="22" t="n"/>
+      <c r="H36" s="23" t="n"/>
       <c r="I36" s="9">
         <f>G35*H35</f>
         <v/>

--- a/docs/printable/金湖展贸中心-设备BOM清单-2026-05-21.xlsx
+++ b/docs/printable/金湖展贸中心-设备BOM清单-2026-05-21.xlsx
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="D8" s="9">
-        <f>'4-音响'!I14</f>
+        <f>'4-音响'!I30</f>
         <v/>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -4176,7 +4176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4206,7 +4206,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4356,51 +4355,16 @@
           <t>LED-RECV</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>LED 接收卡 (按张计)</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>诺瓦星云</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>NovaStar</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>A4s / A8s</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="I8" s="9">
-        <f>G9*H9</f>
-        <v/>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>每张接 65 万像素 LED 模组, 数量按屏估算</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>屏幕内部</t>
-        </is>
-      </c>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="23" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -4493,7 +4457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4512,14 +4476,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>金湖展贸中心智能控制系统 · 4. 音响子系统</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
+          <t>金湖展贸中心智能控制系统 · 4. 音响子系统 (按 AUDIO_ARCHITECTURE.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>BOM 物料明细 · 更新日期 2026-05-21</t>
+          <t>DSP MAG6864 (8 路) · LED 大屏影院音效 · 讲解员跟随式 · 会议室独立 · 更新 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -4583,19 +4547,9 @@
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>4.1 DSP 数字音频处理器</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
-      <c r="E5" s="22" t="n"/>
-      <c r="F5" s="22" t="n"/>
-      <c r="G5" s="22" t="n"/>
-      <c r="H5" s="22" t="n"/>
-      <c r="I5" s="22" t="n"/>
-      <c r="J5" s="22" t="n"/>
-      <c r="K5" s="23" t="n"/>
+          <t>4.1 DSP 数字音频处理器 (8 路矩阵)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -4610,7 +4564,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>数字音频处理器 (DSP)</t>
+          <t>8 路数字音频处理器 (DSP 矩阵)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -4625,14 +4579,14 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>MAG6816</t>
+          <t>MAG6864</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>3200</v>
+        <v>6000</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -4640,7 +4594,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>4 路分区输出 · 网络控制 · MIC 优先压低</t>
+          <t>8 路输出 · 4 MIC + 2 AUX 输入 · 矩阵路由 · 网络控制</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
@@ -4652,24 +4606,14 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>4.2 功放与喇叭</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="23" t="n"/>
+          <t>4.2 LED 大屏区影院级音效 (★ ZONE 1)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>AUDIO-AMP</t>
+          <t>AUDIO-AMP-LED</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -4679,26 +4623,26 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>定阻功放 (按分区配)</t>
+          <t>LED 大屏区 大功率立体声功放</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>同 DSP 品牌</t>
+          <t>迪士普</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DSPPA</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>按功率匹配 (推荐 4Ω/100W)</t>
+          <t>MP-8500U (500W 立体声)</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>1800</v>
@@ -4709,19 +4653,19 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>每个分区 1 台, 共 4 区</t>
+          <t>推 2 只全频主音箱 + 低音炮 · 接 DSP OUT 1</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>1F 弱电机柜</t>
+          <t>1F 主控室机柜</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>AUDIO-SPK</t>
+          <t>AUDIO-SPK-MAIN</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -4731,29 +4675,29 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>吸顶喇叭 (按区域配)</t>
+          <t>LED 大屏 全频主音箱 (左)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>吸顶 6.5"/8" 或壁挂 30-60W</t>
+          <t>Control 28-1 (8" 2 分频)</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="I9" s="9">
         <f>G9*H9</f>
@@ -4761,36 +4705,71 @@
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>按区域天花/墙面布置</t>
+          <t>左声道, 落地/吊装 · 跟 LED 屏对齐</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>各区域天花/墙面</t>
+          <t>1F LED 大屏左侧</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>4.3 麦克风 (无线 UHF, 推荐方案见 docs/WIRELESS_NETWORK.md)</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="22" t="n"/>
-      <c r="I10" s="22" t="n"/>
-      <c r="J10" s="22" t="n"/>
-      <c r="K10" s="23" t="n"/>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO-SPK-MAIN</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>音响</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>LED 大屏 全频主音箱 (右)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Control 28-1 (8" 2 分频)</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I10" s="9">
+        <f>G10*H10</f>
+        <v/>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>右声道, 落地/吊装</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>1F LED 大屏右侧</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>AUDIO-MIC-1</t>
+          <t>AUDIO-SPK-SUB</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -4800,29 +4779,29 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>无线手持麦克风 (一拖二)</t>
+          <t>LED 大屏 主动低音炮</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>舒尔</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Shure</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>BLX24/PG58</t>
+          <t>CSS-SUB12 (12" 主动)</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="I11" s="9">
         <f>G11*H11</f>
@@ -4830,71 +4809,26 @@
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>UHF 470-510 MHz · 2 支手持</t>
+          <t>影院级低频, 视频音轨用</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>接待区/路演区</t>
+          <t>1F LED 大屏侧 / 桌下</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>AUDIO-MIC-2</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>音响</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>无线腰挂领夹麦 (可选)</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>得胜</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Takstar</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>TS-9550</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I12" s="9">
-        <f>G12*H12</f>
-        <v/>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>UHF 国标 · 导览/路演移动用 (可选)</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>路演区</t>
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>4.3 通用分区音响 (ZONE 2-7, 6 个区)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>AUDIO-MIC-3</t>
+          <t>AUDIO-AMP-Z2</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -4904,29 +4838,29 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>鹅颈会议麦 (可选, 接待用)</t>
+          <t>路演区功放</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>舒尔</t>
+          <t>迪士普</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Shure</t>
+          <t>DSPPA</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>MX418</t>
+          <t>MP-120U (120W)</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>3500</v>
+        <v>600</v>
       </c>
       <c r="I13" s="9">
         <f>G13*H13</f>
@@ -4934,41 +4868,734 @@
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>主席台会议用 (可选)</t>
+          <t>接 DSP OUT 2, 推 4 只吸顶</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>2F 会议室</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+          <t>1F 弱电机柜</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO-AMP-Z3</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>音响</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>1F 前厅+走廊功放</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>迪士普</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DSPPA</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>MP-120U</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>600</v>
+      </c>
+      <c r="I14" s="9">
+        <f>G14*H14</f>
+        <v/>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>接 DSP OUT 3, 推 6 只吸顶</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>1F 弱电机柜</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO-AMP-Z4</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>音响</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>1F 展位群功放</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>迪士普</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>DSPPA</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>MP-120U</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>600</v>
+      </c>
+      <c r="I15" s="9">
+        <f>G15*H15</f>
+        <v/>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>接 DSP OUT 4, 推 6 只吸顶</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>1F 弱电机柜</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO-AMP-Z5</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>音响</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>2F 前厅+服务功放</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>迪士普</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DSPPA</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>MP-120U</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>600</v>
+      </c>
+      <c r="I16" s="9">
+        <f>G16*H16</f>
+        <v/>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>接 DSP OUT 5, 推 4 只吸顶</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>2F F201 电箱</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO-AMP-Z6</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>音响</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>2F 商务办公功放</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>迪士普</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>DSPPA</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>MP-120U</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>600</v>
+      </c>
+      <c r="I17" s="9">
+        <f>G17*H17</f>
+        <v/>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>接 DSP OUT 6, 推 4 只吸顶 (集团/决策/研究/指挥)</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>2F F201/F203 电箱</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO-AMP-Z7</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>音响</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>2F 共享办公功放</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>迪士普</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DSPPA</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>MP-120U</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>600</v>
+      </c>
+      <c r="I18" s="9">
+        <f>G18*H18</f>
+        <v/>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>接 DSP OUT 7, 推 4 只吸顶</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>2F F202 电箱</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO-SPK-ZONE</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>音响</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>通用吸顶喇叭 (ZONE 2-7 共用)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>迪士普</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DSPPA</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>DSP-625 / DSP-825 (6.5"/8" 50W)</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>250</v>
+      </c>
+      <c r="I19" s="9">
+        <f>G19*H19</f>
+        <v/>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>各分区按需布置 (路演 4 + 1F 前厅 6 + 1F 展位 6 + 2F 前厅 4 + 商务 4)</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>各区域天花</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>4.4 会议室独立 (★ ZONE 8, 物理隔离)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO-AMP-MEET</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>音响</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>会议室独立功放</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>迪士普</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>DSPPA</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>MP-200U (200W)</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>800</v>
+      </c>
+      <c r="I21" s="9">
+        <f>G21*H21</f>
+        <v/>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>接 DSP OUT 8, 推 4 只会议吸顶</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>会议室或 2F 弱电箱</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO-SPK-MEET</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>音响</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>会议室高品质吸顶喇叭</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Control 25-1 (5.25")</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>800</v>
+      </c>
+      <c r="I22" s="9">
+        <f>G22*H22</f>
+        <v/>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>会议级清晰度, 主席台前后排</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>会议室天花</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO-HDMI-EXT-MEET</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>音响</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>会议室笔记本 HDMI 抽音器</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>4K HDMI Audio Extractor</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="I23" s="9">
+        <f>G23*H23</f>
+        <v/>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>会议笔记本 HDMI 接入 DSP MUSIC 2</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>会议室</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>4.5 麦克风 (UHF 470-525 MHz 国标频段)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO-MIC-GUIDE</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>音响</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>讲解员无线麦 (一拖二)</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>舒尔</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Shure</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>BLX24/PG58</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I25" s="9">
+        <f>G25*H25</f>
+        <v/>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>主用 + 备用手持 · 跟随式路由用</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>讲解员携带</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO-MIC-MEET-W</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>音响</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>会议室无线麦 (一拖二)</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>舒尔</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Shure</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>BLX24/PG58</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I26" s="9">
+        <f>G26*H26</f>
+        <v/>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>会议手持 · 独立路由不被讲解员路由波及</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>会议室</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO-MIC-MEET-G</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>音响</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>会议室鹅颈麦 (主席台)</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>舒尔</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Shure</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>MX418</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I27" s="9">
+        <f>G27*H27</f>
+        <v/>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>主席台正副位 · XLR 接入 DSP</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>会议室主席台</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>4.6 GK9000 ↔ DSP 抽音 (LED 大屏视频音轨)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO-USB-CARD</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>音响</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>USB 外置声卡 (GK9000 → DSP 抽音)</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>创新 / 福克斯</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Creative / Focusrite</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Sound Blaster X3 或 Scarlett 2i2</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I29" s="9">
+        <f>G29*H29</f>
+        <v/>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>GK9000 USB 输出, 3.5mm/XLR 接入 DSP MUSIC 1, 信噪比好</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>1F 主控室机柜</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>本表合计</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="22" t="n"/>
-      <c r="F14" s="22" t="n"/>
-      <c r="G14" s="22" t="n"/>
-      <c r="H14" s="23" t="n"/>
-      <c r="I14" s="20">
-        <f>SUM(I5:I13)</f>
-        <v/>
-      </c>
-      <c r="J14" s="21" t="n"/>
-      <c r="K14" s="21" t="n"/>
+      <c r="I30" s="20">
+        <f>SUM(I5:I29)</f>
+        <v/>
+      </c>
+      <c r="J30" s="21" t="n"/>
+      <c r="K30" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A20:K20"/>
     <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A24:K24"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A28:K28"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>

--- a/docs/printable/金湖展贸中心-设备BOM清单-2026-05-21.xlsx
+++ b/docs/printable/金湖展贸中心-设备BOM清单-2026-05-21.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>音响 (DSP + 功放 + 喇叭 + 麦克风)</t>
+          <t>音响 (得胜混搭: DSP/麦/通用得胜 + 影音 JBL)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>DSPPA MAG6816 + 4 区 + 舒尔无线麦</t>
+          <t>得胜 EKX-408 + JBL Control 28-1/SUB12 + 得胜 TS-8808HH × 2 + 得胜 MS-189 × 2</t>
         </is>
       </c>
     </row>
@@ -4476,14 +4476,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>金湖展贸中心智能控制系统 · 4. 音响子系统 (按 AUDIO_ARCHITECTURE.md)</t>
+          <t>金湖展贸中心智能控制系统 · 4. 音响子系统 (得胜混搭方案)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>DSP MAG6864 (8 路) · LED 大屏影院音效 · 讲解员跟随式 · 会议室独立 · 更新 2026-05-21</t>
+          <t>得胜 EKX-408 DSP + 公共广播 + UHF 无线麦 · 影音重头戏保 JBL · 总价 ¥27,700 (省 ¥17K) · 更新 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>4.1 DSP 数字音频处理器 (8 路矩阵)</t>
+          <t>4.1 DSP 数字音频处理器 (得胜国产, 替代 DSPPA MAG6864)</t>
         </is>
       </c>
     </row>
@@ -4564,29 +4564,29 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>8 路数字音频处理器 (DSP 矩阵)</t>
+          <t>数字音频处理器 (4 进 8 出)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>迪士普</t>
+          <t>得胜</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>DSPPA</t>
+          <t>TAKSTAR</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>MAG6864</t>
+          <t>EKX-408</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>6000</v>
+        <v>3500</v>
       </c>
       <c r="I6" s="9">
         <f>G6*H6</f>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>8 路输出 · 4 MIC + 2 AUX 输入 · 矩阵路由 · 网络控制</t>
+          <t>4 输入 + 8 输出矩阵 · USB/RS485/TCP-IP · 96kHz 32-bit DSP · 国产替代 DSPPA MAG6864</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
@@ -4606,7 +4606,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>4.2 LED 大屏区影院级音效 (★ ZONE 1)</t>
+          <t>4.2 LED 大屏区影院级音效 (★ ZONE 1, 保 JBL 影音)</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>推 2 只全频主音箱 + 低音炮 · 接 DSP OUT 1</t>
+          <t>推 2 只全频主音箱 + 低音炮 · 得胜无同档大功率立体声款, 保 DSPPA</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>左声道, 落地/吊装 · 跟 LED 屏对齐</t>
+          <t>左声道, 影院级, 落地/吊装 · 得胜无同档款保 JBL</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>右声道, 落地/吊装</t>
+          <t>右声道</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>影院级低频, 视频音轨用</t>
+          <t>影院级低频, 视频音轨用 · 得胜无同档款保 JBL</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
@@ -4821,7 +4821,7 @@
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>4.3 通用分区音响 (ZONE 2-7, 6 个区)</t>
+          <t>4.3 通用分区音响 (ZONE 2-7, 6 个区, 得胜国产)</t>
         </is>
       </c>
     </row>
@@ -4838,29 +4838,29 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>路演区功放</t>
+          <t>路演区功放 (120W)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>迪士普</t>
+          <t>得胜</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>DSPPA</t>
+          <t>TAKSTAR</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>MP-120U (120W)</t>
+          <t>公共广播 120W 功放</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I13" s="9">
         <f>G13*H13</f>
@@ -4890,29 +4890,29 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>1F 前厅+走廊功放</t>
+          <t>1F 前厅+走廊功放 (120W)</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>迪士普</t>
+          <t>得胜</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>DSPPA</t>
+          <t>TAKSTAR</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>MP-120U</t>
+          <t>公共广播 120W 功放</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I14" s="9">
         <f>G14*H14</f>
@@ -4942,29 +4942,29 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>1F 展位群功放</t>
+          <t>1F 展位群功放 (120W)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>迪士普</t>
+          <t>得胜</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>DSPPA</t>
+          <t>TAKSTAR</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>MP-120U</t>
+          <t>公共广播 120W 功放</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I15" s="9">
         <f>G15*H15</f>
@@ -4994,29 +4994,29 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>2F 前厅+服务功放</t>
+          <t>2F 前厅+服务功放 (120W)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>迪士普</t>
+          <t>得胜</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>DSPPA</t>
+          <t>TAKSTAR</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>MP-120U</t>
+          <t>公共广播 120W 功放</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I16" s="9">
         <f>G16*H16</f>
@@ -5046,29 +5046,29 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>2F 商务办公功放</t>
+          <t>2F 商务办公功放 (120W)</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>迪士普</t>
+          <t>得胜</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>DSPPA</t>
+          <t>TAKSTAR</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>MP-120U</t>
+          <t>公共广播 120W 功放</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I17" s="9">
         <f>G17*H17</f>
@@ -5098,29 +5098,29 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>2F 共享办公功放</t>
+          <t>2F 共享办公功放 (120W)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>迪士普</t>
+          <t>得胜</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>DSPPA</t>
+          <t>TAKSTAR</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>MP-120U</t>
+          <t>公共广播 120W 功放</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I18" s="9">
         <f>G18*H18</f>
@@ -5150,29 +5150,29 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>通用吸顶喇叭 (ZONE 2-7 共用)</t>
+          <t>通用吸顶喇叭 (6.5"/8" 50W)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>迪士普</t>
+          <t>得胜</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>DSPPA</t>
+          <t>TAKSTAR</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>DSP-625 / DSP-825 (6.5"/8" 50W)</t>
+          <t>公共广播 6.5"/8" 50W 吸顶</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
         <v>24</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="I19" s="9">
         <f>G19*H19</f>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>各分区按需布置 (路演 4 + 1F 前厅 6 + 1F 展位 6 + 2F 前厅 4 + 商务 4)</t>
+          <t>各分区按布置 (路演 4 + 1F 前厅 6 + 1F 展位 6 + 2F 前厅 4 + 商务 4)</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
@@ -5192,7 +5192,7 @@
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>4.4 会议室独立 (★ ZONE 8, 物理隔离)</t>
+          <t>4.4 会议室独立 (★ ZONE 8, 保 JBL 高品质吸顶)</t>
         </is>
       </c>
     </row>
@@ -5209,29 +5209,29 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>会议室独立功放</t>
+          <t>会议室独立功放 (200W)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>迪士普</t>
+          <t>得胜</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>DSPPA</t>
+          <t>TAKSTAR</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>MP-200U (200W)</t>
+          <t>公共广播 200W 功放</t>
         </is>
       </c>
       <c r="G21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="I21" s="9">
         <f>G21*H21</f>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>接 DSP OUT 8, 推 4 只会议吸顶</t>
+          <t>接 DSP OUT 8, 推 4 只 JBL 会议吸顶</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>会议室高品质吸顶喇叭</t>
+          <t>会议室 高品质吸顶喇叭 (★ 保 JBL)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>会议级清晰度, 主席台前后排</t>
+          <t>会议级清晰度 · 得胜公共广播喇叭清晰度不够, 保 JBL</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
@@ -5355,7 +5355,7 @@
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>4.5 麦克风 (UHF 470-525 MHz 国标频段)</t>
+          <t>4.5 麦克风 (得胜全套, UHF 国标 470-525 MHz)</t>
         </is>
       </c>
     </row>
@@ -5372,29 +5372,29 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>讲解员无线麦 (一拖二)</t>
+          <t>讲解员无线麦 (一拖二, UHF 真分集)</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>舒尔</t>
+          <t>得胜</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Shure</t>
+          <t>TAKSTAR</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>BLX24/PG58</t>
+          <t>TS-8808HH</t>
         </is>
       </c>
       <c r="G25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>5000</v>
+        <v>1200</v>
       </c>
       <c r="I25" s="9">
         <f>G25*H25</f>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>主用 + 备用手持 · 跟随式路由用</t>
+          <t>主用 + 备用手持 · 跟随式路由用 · 国产替代舒尔 BLX24</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
@@ -5429,24 +5429,24 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>舒尔</t>
+          <t>得胜</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Shure</t>
+          <t>TAKSTAR</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>BLX24/PG58</t>
+          <t>TS-8808HH</t>
         </is>
       </c>
       <c r="G26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>5000</v>
+        <v>1200</v>
       </c>
       <c r="I26" s="9">
         <f>G26*H26</f>
@@ -5481,24 +5481,24 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>舒尔</t>
+          <t>得胜</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Shure</t>
+          <t>TAKSTAR</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>MX418</t>
+          <t>MS-189 (台式鹅颈)</t>
         </is>
       </c>
       <c r="G27" s="7" t="n">
         <v>2</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>3500</v>
+        <v>400</v>
       </c>
       <c r="I27" s="9">
         <f>G27*H27</f>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>主席台正副位 · XLR 接入 DSP</t>
+          <t>心形指向 · XLR 接 DSP · 国产替代舒尔 MX418</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
@@ -5577,7 +5577,7 @@
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>本表合计</t>
+          <t>本表合计 (得胜混搭, 省 ¥1.7 万)</t>
         </is>
       </c>
       <c r="I30" s="20">
